--- a/Samples/Sample_Timetable.xlsx
+++ b/Samples/Sample_Timetable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikhi\OneDrive\Desktop\Teacher App v1.3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikhi\OneDrive\Desktop\v1.5.1\Samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A11D7A-10BB-4096-AF58-CA794937443E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD2FFB0-F016-467A-86C9-E935500160B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="18">
   <si>
     <t>Day</t>
   </si>
@@ -37,18 +37,9 @@
     <t>XI-A</t>
   </si>
   <si>
-    <t>CS</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
     <t>XI-B</t>
   </si>
   <si>
-    <t>AI</t>
-  </si>
-  <si>
     <t>FREE</t>
   </si>
   <si>
@@ -65,6 +56,24 @@
   </si>
   <si>
     <t>Monday</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Sub</t>
   </si>
 </sst>
 </file>
@@ -433,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
@@ -455,58 +464,58 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -514,52 +523,161 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B9">
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
         <v>8</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>12</v>
       </c>
-      <c r="D9" t="s">
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
         <v>5</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
